--- a/Result/profitability/9910.xlsx
+++ b/Result/profitability/9910.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15</v>
+        <v>1.09875</v>
       </c>
       <c r="N2" t="n">
-        <v>21.35125</v>
+        <v>20.82</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>1.00625</v>
+        <v>0.93375</v>
       </c>
       <c r="N3" t="n">
-        <v>20.6175</v>
+        <v>20.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0.86</v>
+        <v>0.84375</v>
       </c>
       <c r="N4" t="n">
-        <v>20.135</v>
+        <v>19.925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8037500000000001</v>
+        <v>0.8412499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>19.8125</v>
+        <v>19.22</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.79</v>
       </c>
       <c r="M6" t="n">
-        <v>0.81125</v>
+        <v>0.72</v>
       </c>
       <c r="N6" t="n">
-        <v>19.71</v>
+        <v>19.17375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.77</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6875</v>
+        <v>0.635</v>
       </c>
       <c r="N7" t="n">
-        <v>19.78625</v>
+        <v>19.62</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6075</v>
+        <v>0.65125</v>
       </c>
       <c r="N8" t="n">
-        <v>20.2425</v>
+        <v>20.4975</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.71</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6112500000000001</v>
+        <v>0.61125</v>
       </c>
       <c r="N9" t="n">
         <v>20.705</v>
@@ -1899,7 +1899,7 @@
         <v>0.88</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7775</v>
+        <v>0.7775000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>20.75125</v>
@@ -2026,7 +2026,7 @@
         <v>0.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7637499999999999</v>
+        <v>0.76375</v>
       </c>
       <c r="N13" t="n">
         <v>20.8475</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9910</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>20380</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16420</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3960</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1206</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.92%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>204</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1410</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1014</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.2325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.64875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5147058823529411</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.039999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1173087981598619</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4109589041095891</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.740000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1961108812577577</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
